--- a/data/stocks/CZStocks.xlsx
+++ b/data/stocks/CZStocks.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,6 +470,11 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Z-Score</t>
         </is>
       </c>
@@ -495,7 +500,10 @@
       <c r="H2" t="n">
         <v>1685.28</v>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>2006</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -523,6 +531,9 @@
         <v>2064.9</v>
       </c>
       <c r="I3" t="n">
+        <v>2007</v>
+      </c>
+      <c r="J3" t="n">
         <v>0.39822896227347</v>
       </c>
     </row>
@@ -552,6 +563,9 @@
         <v>1928.86</v>
       </c>
       <c r="I4" t="n">
+        <v>2008</v>
+      </c>
+      <c r="J4" t="n">
         <v>-2.65162730097534</v>
       </c>
     </row>
@@ -581,6 +595,9 @@
         <v>1384.13</v>
       </c>
       <c r="I5" t="n">
+        <v>2009</v>
+      </c>
+      <c r="J5" t="n">
         <v>1.296981240646177</v>
       </c>
     </row>
@@ -610,6 +627,9 @@
         <v>1548.31</v>
       </c>
       <c r="I6" t="n">
+        <v>2010</v>
+      </c>
+      <c r="J6" t="n">
         <v>0.2756151895233061</v>
       </c>
     </row>
@@ -639,6 +659,9 @@
         <v>1589.37</v>
       </c>
       <c r="I7" t="n">
+        <v>2011</v>
+      </c>
+      <c r="J7" t="n">
         <v>-1.330647486457151</v>
       </c>
     </row>
@@ -668,6 +691,9 @@
         <v>1401.33</v>
       </c>
       <c r="I8" t="n">
+        <v>2012</v>
+      </c>
+      <c r="J8" t="n">
         <v>0.4328545576272366</v>
       </c>
     </row>
@@ -697,6 +723,9 @@
         <v>1462.96</v>
       </c>
       <c r="I9" t="n">
+        <v>2013</v>
+      </c>
+      <c r="J9" t="n">
         <v>-0.4099092902120014</v>
       </c>
     </row>
@@ -726,6 +755,9 @@
         <v>1493.81</v>
       </c>
       <c r="I10" t="n">
+        <v>2014</v>
+      </c>
+      <c r="J10" t="n">
         <v>-0.3975811540770485</v>
       </c>
     </row>
@@ -755,6 +787,9 @@
         <v>1585.38</v>
       </c>
       <c r="I11" t="n">
+        <v>2015</v>
+      </c>
+      <c r="J11" t="n">
         <v>-0.1548459393476862</v>
       </c>
     </row>
@@ -784,6 +819,9 @@
         <v>1511.49</v>
       </c>
       <c r="I12" t="n">
+        <v>2016</v>
+      </c>
+      <c r="J12" t="n">
         <v>-0.3046528210453454</v>
       </c>
     </row>
@@ -813,6 +851,9 @@
         <v>1845.17</v>
       </c>
       <c r="I13" t="n">
+        <v>2017</v>
+      </c>
+      <c r="J13" t="n">
         <v>0.6663770496853526</v>
       </c>
     </row>
@@ -842,6 +883,9 @@
         <v>1993.76</v>
       </c>
       <c r="I14" t="n">
+        <v>2018</v>
+      </c>
+      <c r="J14" t="n">
         <v>-0.5404006084346803</v>
       </c>
     </row>
@@ -871,6 +915,9 @@
         <v>2119.45</v>
       </c>
       <c r="I15" t="n">
+        <v>2019</v>
+      </c>
+      <c r="J15" t="n">
         <v>0.481766549007429</v>
       </c>
     </row>
@@ -900,6 +947,9 @@
         <v>2163.35</v>
       </c>
       <c r="I16" t="n">
+        <v>2020</v>
+      </c>
+      <c r="J16" t="n">
         <v>-0.6043110903472882</v>
       </c>
     </row>
@@ -929,6 +979,9 @@
         <v>2918.25</v>
       </c>
       <c r="I17" t="n">
+        <v>2021</v>
+      </c>
+      <c r="J17" t="n">
         <v>1.638920121241279</v>
       </c>
     </row>
@@ -958,6 +1011,9 @@
         <v>3045.53</v>
       </c>
       <c r="I18" t="n">
+        <v>2022</v>
+      </c>
+      <c r="J18" t="n">
         <v>-0.7869188252271148</v>
       </c>
     </row>
@@ -987,6 +1043,9 @@
         <v>3398.83</v>
       </c>
       <c r="I19" t="n">
+        <v>2023</v>
+      </c>
+      <c r="J19" t="n">
         <v>0.8680778185070376</v>
       </c>
     </row>
@@ -1016,6 +1075,9 @@
         <v>4567.91</v>
       </c>
       <c r="I20" t="n">
+        <v>2024</v>
+      </c>
+      <c r="J20" t="n">
         <v>1.122073027612368</v>
       </c>
     </row>

--- a/data/stocks/CZStocks.xlsx
+++ b/data/stocks/CZStocks.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,610 +475,608 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Log_return</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Z-Score</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>39082</v>
+        <v>39447</v>
       </c>
       <c r="C2" t="n">
-        <v>1646.73</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+        <v>1935.81</v>
+      </c>
+      <c r="D2" t="n">
+        <v>289.08</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.17555</v>
+      </c>
       <c r="F2" t="n">
-        <v>1554.6</v>
+        <v>1677.17</v>
       </c>
       <c r="G2" t="n">
-        <v>1188.44</v>
+        <v>1622.21</v>
       </c>
       <c r="H2" t="n">
-        <v>1685.28</v>
+        <v>2064.9</v>
       </c>
       <c r="I2" t="n">
-        <v>2006</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
+        <v>2007</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.1617</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.4333787771834243</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>39447</v>
+        <v>40178</v>
       </c>
       <c r="C3" t="n">
-        <v>1935.81</v>
+        <v>1307.35</v>
       </c>
       <c r="D3" t="n">
-        <v>289.08</v>
+        <v>358.27</v>
       </c>
       <c r="E3" t="n">
-        <v>0.17555</v>
+        <v>0.37749</v>
       </c>
       <c r="F3" t="n">
-        <v>1677.17</v>
+        <v>962.25</v>
       </c>
       <c r="G3" t="n">
-        <v>1622.21</v>
+        <v>695.02</v>
       </c>
       <c r="H3" t="n">
-        <v>2064.9</v>
+        <v>1384.13</v>
       </c>
       <c r="I3" t="n">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="J3" t="n">
-        <v>0.39822896227347</v>
+        <v>0.3203</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.086053251283044</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>39813</v>
+        <v>40543</v>
       </c>
       <c r="C4" t="n">
-        <v>949.08</v>
+        <v>1500.84</v>
       </c>
       <c r="D4" t="n">
-        <v>-986.73</v>
+        <v>193.49</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.50972</v>
+        <v>0.148</v>
       </c>
       <c r="F4" t="n">
-        <v>1928.86</v>
+        <v>1325.09</v>
       </c>
       <c r="G4" t="n">
-        <v>773.84</v>
+        <v>1278.71</v>
       </c>
       <c r="H4" t="n">
-        <v>1928.86</v>
+        <v>1548.31</v>
       </c>
       <c r="I4" t="n">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="J4" t="n">
-        <v>-2.65162730097534</v>
+        <v>0.138</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.3358479761988026</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>40178</v>
+        <v>40908</v>
       </c>
       <c r="C5" t="n">
-        <v>1307.35</v>
+        <v>1181.29</v>
       </c>
       <c r="D5" t="n">
-        <v>358.27</v>
+        <v>-319.55</v>
       </c>
       <c r="E5" t="n">
-        <v>0.37749</v>
+        <v>-0.21291</v>
       </c>
       <c r="F5" t="n">
-        <v>962.25</v>
+        <v>1523.62</v>
       </c>
       <c r="G5" t="n">
-        <v>695.02</v>
+        <v>1093.06</v>
       </c>
       <c r="H5" t="n">
-        <v>1384.13</v>
+        <v>1589.37</v>
       </c>
       <c r="I5" t="n">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="J5" t="n">
-        <v>1.296981240646177</v>
+        <v>-0.2394</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-1.217237436948717</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>40543</v>
+        <v>41274</v>
       </c>
       <c r="C6" t="n">
-        <v>1500.84</v>
+        <v>1397.85</v>
       </c>
       <c r="D6" t="n">
-        <v>193.49</v>
+        <v>216.56</v>
       </c>
       <c r="E6" t="n">
-        <v>0.148</v>
+        <v>0.18333</v>
       </c>
       <c r="F6" t="n">
-        <v>1325.09</v>
+        <v>1197.6</v>
       </c>
       <c r="G6" t="n">
-        <v>1278.71</v>
+        <v>1131.29</v>
       </c>
       <c r="H6" t="n">
-        <v>1548.31</v>
+        <v>1401.33</v>
       </c>
       <c r="I6" t="n">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2756151895233061</v>
+        <v>0.1683</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.4605392534069898</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>40908</v>
+        <v>41639</v>
       </c>
       <c r="C7" t="n">
-        <v>1181.29</v>
+        <v>1389.42</v>
       </c>
       <c r="D7" t="n">
-        <v>-319.55</v>
+        <v>-8.43</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.21291</v>
+        <v>-0.00603</v>
       </c>
       <c r="F7" t="n">
-        <v>1523.62</v>
+        <v>1434.6</v>
       </c>
       <c r="G7" t="n">
-        <v>1093.06</v>
+        <v>1187.86</v>
       </c>
       <c r="H7" t="n">
-        <v>1589.37</v>
+        <v>1462.96</v>
       </c>
       <c r="I7" t="n">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.330647486457151</v>
+        <v>-0.006</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0.2567442323153543</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>41274</v>
+        <v>42004</v>
       </c>
       <c r="C8" t="n">
-        <v>1397.85</v>
+        <v>1384.89</v>
       </c>
       <c r="D8" t="n">
-        <v>216.56</v>
+        <v>-4.53</v>
       </c>
       <c r="E8" t="n">
-        <v>0.18333</v>
+        <v>-0.00326</v>
       </c>
       <c r="F8" t="n">
-        <v>1197.6</v>
+        <v>1396.17</v>
       </c>
       <c r="G8" t="n">
-        <v>1131.29</v>
+        <v>1299.9</v>
       </c>
       <c r="H8" t="n">
-        <v>1401.33</v>
+        <v>1493.81</v>
       </c>
       <c r="I8" t="n">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4328545576272366</v>
+        <v>-0.0033</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-0.2456331284057138</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>41639</v>
+        <v>42369</v>
       </c>
       <c r="C9" t="n">
-        <v>1389.42</v>
+        <v>1455.91</v>
       </c>
       <c r="D9" t="n">
-        <v>-8.43</v>
+        <v>71.02</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.00603</v>
+        <v>0.05128</v>
       </c>
       <c r="F9" t="n">
-        <v>1434.6</v>
+        <v>1383.87</v>
       </c>
       <c r="G9" t="n">
-        <v>1187.86</v>
+        <v>1364.46</v>
       </c>
       <c r="H9" t="n">
-        <v>1462.96</v>
+        <v>1585.38</v>
       </c>
       <c r="I9" t="n">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.4099092902120014</v>
+        <v>0.05</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-0.02629170678207103</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>42004</v>
+        <v>42735</v>
       </c>
       <c r="C10" t="n">
-        <v>1384.89</v>
+        <v>1481.56</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.53</v>
+        <v>25.65</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.00326</v>
+        <v>0.01762</v>
       </c>
       <c r="F10" t="n">
-        <v>1396.17</v>
+        <v>1452.63</v>
       </c>
       <c r="G10" t="n">
-        <v>1299.9</v>
+        <v>1234.58</v>
       </c>
       <c r="H10" t="n">
-        <v>1493.81</v>
+        <v>1511.49</v>
       </c>
       <c r="I10" t="n">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3975811540770485</v>
+        <v>0.0175</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0.1600364760647801</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>42369</v>
+        <v>43100</v>
       </c>
       <c r="C11" t="n">
-        <v>1455.91</v>
+        <v>1830.91</v>
       </c>
       <c r="D11" t="n">
-        <v>71.02</v>
+        <v>349.35</v>
       </c>
       <c r="E11" t="n">
-        <v>0.05128</v>
+        <v>0.2358</v>
       </c>
       <c r="F11" t="n">
-        <v>1383.87</v>
+        <v>1481.59</v>
       </c>
       <c r="G11" t="n">
-        <v>1364.46</v>
+        <v>1476.75</v>
       </c>
       <c r="H11" t="n">
-        <v>1585.38</v>
+        <v>1845.17</v>
       </c>
       <c r="I11" t="n">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1548459393476862</v>
+        <v>0.2117</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.6391399606952843</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>42735</v>
+        <v>43465</v>
       </c>
       <c r="C12" t="n">
-        <v>1481.56</v>
+        <v>1766.18</v>
       </c>
       <c r="D12" t="n">
-        <v>25.65</v>
+        <v>-64.73</v>
       </c>
       <c r="E12" t="n">
-        <v>0.01762</v>
+        <v>-0.03535</v>
       </c>
       <c r="F12" t="n">
-        <v>1452.63</v>
+        <v>1830.89</v>
       </c>
       <c r="G12" t="n">
-        <v>1234.58</v>
+        <v>1746.05</v>
       </c>
       <c r="H12" t="n">
-        <v>1511.49</v>
+        <v>1993.76</v>
       </c>
       <c r="I12" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3046528210453454</v>
+        <v>-0.036</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-0.3802009424224703</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>43100</v>
+        <v>43830</v>
       </c>
       <c r="C13" t="n">
-        <v>1830.91</v>
+        <v>2109.39</v>
       </c>
       <c r="D13" t="n">
-        <v>349.35</v>
+        <v>343.21</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2358</v>
+        <v>0.19432</v>
       </c>
       <c r="F13" t="n">
-        <v>1481.59</v>
+        <v>1768.23</v>
       </c>
       <c r="G13" t="n">
-        <v>1476.75</v>
+        <v>1763.17</v>
       </c>
       <c r="H13" t="n">
-        <v>1845.17</v>
+        <v>2119.45</v>
       </c>
       <c r="I13" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6663770496853526</v>
+        <v>0.1776</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.4988108335401958</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>43465</v>
+        <v>44196</v>
       </c>
       <c r="C14" t="n">
-        <v>1766.18</v>
+        <v>2004.54</v>
       </c>
       <c r="D14" t="n">
-        <v>-64.73</v>
+        <v>-104.85</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.03535</v>
+        <v>-0.04971</v>
       </c>
       <c r="F14" t="n">
-        <v>1830.89</v>
+        <v>2110.18</v>
       </c>
       <c r="G14" t="n">
-        <v>1746.05</v>
+        <v>1306.01</v>
       </c>
       <c r="H14" t="n">
-        <v>1993.76</v>
+        <v>2163.35</v>
       </c>
       <c r="I14" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.5404006084346803</v>
+        <v>-0.051</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-0.4419292974760283</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>43830</v>
+        <v>44561</v>
       </c>
       <c r="C15" t="n">
-        <v>2109.39</v>
+        <v>2915.25</v>
       </c>
       <c r="D15" t="n">
-        <v>343.21</v>
+        <v>910.71</v>
       </c>
       <c r="E15" t="n">
-        <v>0.19432</v>
+        <v>0.45432</v>
       </c>
       <c r="F15" t="n">
-        <v>1768.23</v>
+        <v>2006.6</v>
       </c>
       <c r="G15" t="n">
-        <v>1763.17</v>
+        <v>1976.32</v>
       </c>
       <c r="H15" t="n">
-        <v>2119.45</v>
+        <v>2918.25</v>
       </c>
       <c r="I15" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="J15" t="n">
-        <v>0.481766549007429</v>
+        <v>0.3745</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.309098374209901</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>44196</v>
+        <v>44926</v>
       </c>
       <c r="C16" t="n">
-        <v>2004.54</v>
+        <v>2650.72</v>
       </c>
       <c r="D16" t="n">
-        <v>-104.85</v>
+        <v>-264.53</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.04971</v>
+        <v>-0.09074</v>
       </c>
       <c r="F16" t="n">
-        <v>2110.18</v>
+        <v>2915.47</v>
       </c>
       <c r="G16" t="n">
-        <v>1306.01</v>
+        <v>2389.92</v>
       </c>
       <c r="H16" t="n">
-        <v>2163.35</v>
+        <v>3045.53</v>
       </c>
       <c r="I16" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.6043110903472882</v>
+        <v>-0.0951</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-0.6234106613334889</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="C17" t="n">
-        <v>2915.25</v>
+        <v>3395.89</v>
       </c>
       <c r="D17" t="n">
-        <v>910.71</v>
+        <v>745.17</v>
       </c>
       <c r="E17" t="n">
-        <v>0.45432</v>
+        <v>0.28112</v>
       </c>
       <c r="F17" t="n">
-        <v>2006.6</v>
+        <v>2650.88</v>
       </c>
       <c r="G17" t="n">
-        <v>1976.32</v>
+        <v>2650.88</v>
       </c>
       <c r="H17" t="n">
-        <v>2918.25</v>
+        <v>3398.83</v>
       </c>
       <c r="I17" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="J17" t="n">
-        <v>1.638920121241279</v>
+        <v>0.2477</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.7872880128238235</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>44926</v>
+        <v>45657</v>
       </c>
       <c r="C18" t="n">
-        <v>2650.72</v>
+        <v>4544.35</v>
       </c>
       <c r="D18" t="n">
-        <v>-264.53</v>
+        <v>1148.46</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.09074</v>
+        <v>0.33819</v>
       </c>
       <c r="F18" t="n">
-        <v>2915.47</v>
+        <v>3396.03</v>
       </c>
       <c r="G18" t="n">
-        <v>2389.92</v>
+        <v>3395.98</v>
       </c>
       <c r="H18" t="n">
-        <v>3045.53</v>
+        <v>4567.91</v>
       </c>
       <c r="I18" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7869188252271148</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>45291</v>
-      </c>
-      <c r="C19" t="n">
-        <v>3395.89</v>
-      </c>
-      <c r="D19" t="n">
-        <v>745.17</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.28112</v>
-      </c>
-      <c r="F19" t="n">
-        <v>2650.88</v>
-      </c>
-      <c r="G19" t="n">
-        <v>2650.88</v>
-      </c>
-      <c r="H19" t="n">
-        <v>3398.83</v>
-      </c>
-      <c r="I19" t="n">
-        <v>2023</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.8680778185070376</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>45657</v>
-      </c>
-      <c r="C20" t="n">
-        <v>4544.35</v>
-      </c>
-      <c r="D20" t="n">
-        <v>1148.46</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.33819</v>
-      </c>
-      <c r="F20" t="n">
-        <v>3396.03</v>
-      </c>
-      <c r="G20" t="n">
-        <v>3395.98</v>
-      </c>
-      <c r="H20" t="n">
-        <v>4567.91</v>
-      </c>
-      <c r="I20" t="n">
-        <v>2024</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1.122073027612368</v>
+        <v>0.2913</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.9667117648461655</v>
       </c>
     </row>
   </sheetData>
